--- a/Medição - Contratada/IRON/Contrato nº 4600686987_Fat._Lote1 - RJ.xlsx
+++ b/Medição - Contratada/IRON/Contrato nº 4600686987_Fat._Lote1 - RJ.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="EstaPastaDeTrabalho"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PainelNovo\Medição - Contratada\IRON\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\Arquivamento_SID\2. Controles\Painel Novo\10-Outubro\Medição - Contratada\IRON\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E2023D9-AB32-48FD-90CC-9B2205C88BBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C07AA35-3ABA-4506-9B85-F8492D213D1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MC IMB RJ" sheetId="1" r:id="rId1"/>
@@ -38,9 +38,6 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId23" roundtripDataChecksum="34oD2PTMo2tTZPMOHyLqYVrzjSBzwU5tr1oSokZuaJ0="/>
@@ -2715,47 +2712,6 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
       <fill>
         <patternFill patternType="none">
@@ -2931,6 +2887,47 @@
           <bgColor theme="9"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <numFmt numFmtId="167" formatCode="&quot;R$&quot;\ #,##0.00"/>
@@ -3628,25 +3625,25 @@
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="$ Total" dataDxfId="16">
       <calculatedColumnFormula>IF(ConsolidadoRJ[[#This Row],[UA]]="","",ConsolidadoRJ[[#This Row],[UA]]*ConsolidadoRJ[[#This Row],[$ Unitário]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Tabela" dataDxfId="2"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Contrato" dataDxfId="1"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Tabela" dataDxfId="15"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Contrato" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{7D024C41-401F-4C7B-8726-35FF674AF416}" name="Padrão" displayName="Padrão" ref="A1:A54" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14" tableBorderDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{7D024C41-401F-4C7B-8726-35FF674AF416}" name="Padrão" displayName="Padrão" ref="A1:A54" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12" tableBorderDxfId="11">
   <autoFilter ref="A1:A54" xr:uid="{7D024C41-401F-4C7B-8726-35FF674AF416}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{FC834546-F8C2-43F1-8653-2C9C306C6853}" name="Padrão" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{FC834546-F8C2-43F1-8653-2C9C306C6853}" name="Padrão" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{C8F13F38-AE54-4F68-8CD4-DFD283E96379}" name="LinhaPPU" displayName="LinhaPPU" ref="E1:E29" totalsRowShown="0" headerRowDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{C8F13F38-AE54-4F68-8CD4-DFD283E96379}" name="LinhaPPU" displayName="LinhaPPU" ref="E1:E29" totalsRowShown="0" headerRowDxfId="9">
   <autoFilter ref="E1:E29" xr:uid="{C8F13F38-AE54-4F68-8CD4-DFD283E96379}"/>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{A3A4CE9E-7B99-4F3C-B222-4D496C2EDC0C}" name="Linha de serviço PPU"/>
@@ -3663,7 +3660,7 @@
     <tableColumn id="3" xr3:uid="{F8835F93-6997-4EE6-A8A2-5BBA9F5F9A23}" name="DESCRIÇÃO"/>
     <tableColumn id="2" xr3:uid="{D294162E-0115-4594-923D-631C31B74466}" name="Linha de Serviço PPU"/>
     <tableColumn id="4" xr3:uid="{A9203A65-B976-413C-97EB-229EAEF64D66}" name="UNID."/>
-    <tableColumn id="6" xr3:uid="{BBC3EA5F-CFDD-489F-BD88-580B0C945906}" name="PREÇO UNITÁRIO " dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{BBC3EA5F-CFDD-489F-BD88-580B0C945906}" name="PREÇO UNITÁRIO " dataDxfId="8"/>
     <tableColumn id="7" xr3:uid="{8FC6BA38-CE26-4D70-9856-F81EFB0A1FF9}" name="Descrição da Linha de Serviço"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -3681,17 +3678,17 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{450CAA71-8558-440D-BD03-9A5B582A67EE}" name="MedidasContrato" displayName="MedidasContrato" ref="N1:R124" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{450CAA71-8558-440D-BD03-9A5B582A67EE}" name="MedidasContrato" displayName="MedidasContrato" ref="N1:R124" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
   <autoFilter ref="N1:R124" xr:uid="{450CAA71-8558-440D-BD03-9A5B582A67EE}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="N2:R124">
     <sortCondition ref="N1:N124"/>
   </sortState>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{848A6E3D-D10C-4C28-A755-1DAD0EF94CF9}" name="MEDIDAS CONTRATO" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{287CB8E4-DBEC-4AE7-A40F-F2A76BFF2D87}" name="Ø" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{38CAEDAB-4961-4068-8C60-2826957DFF9B}" name="A" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{8EAB565D-87A9-4B0E-BCC0-704CC37666E9}" name="L" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{33CC69D2-CED7-4EB1-AF77-D6211E14BE46}" name="P" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{848A6E3D-D10C-4C28-A755-1DAD0EF94CF9}" name="MEDIDAS CONTRATO" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{287CB8E4-DBEC-4AE7-A40F-F2A76BFF2D87}" name="Ø" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{38CAEDAB-4961-4068-8C60-2826957DFF9B}" name="A" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{8EAB565D-87A9-4B0E-BCC0-704CC37666E9}" name="L" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{33CC69D2-CED7-4EB1-AF77-D6211E14BE46}" name="P" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4240,11 +4237,11 @@
       </c>
       <c r="J13" s="40">
         <f>SUMIF(Consolidado!S:S,D12,Consolidado!O:O)</f>
-        <v>207623.99</v>
+        <v>233913.67499999999</v>
       </c>
       <c r="K13" s="41">
         <f>J13*N5</f>
-        <v>203471.51019999999</v>
+        <v>229235.40149999998</v>
       </c>
       <c r="L13" s="42">
         <f>IFERROR(VLOOKUP(ARMCXDOC,TabelaIRON[[Linha de Serviço PPU]:[PREÇO UNITÁRIO ]],3,FALSE),"N/A")</f>
@@ -4252,7 +4249,7 @@
       </c>
       <c r="M13" s="43">
         <f>J13*L13</f>
-        <v>124574.39399999999</v>
+        <v>140348.20499999999</v>
       </c>
       <c r="N13" s="151"/>
       <c r="P13" s="44"/>
@@ -4264,11 +4261,11 @@
       <c r="C14" s="45"/>
       <c r="D14" s="98">
         <f>SUMIF(ConsolidadoRJ[Contrato], D12, ConsolidadoRJ[QUAm-1])</f>
-        <v>184924</v>
+        <v>206009</v>
       </c>
       <c r="E14" s="98">
         <f>SUMIF(ConsolidadoRJ[Contrato], D12, ConsolidadoRJ[QBm])</f>
-        <v>1</v>
+        <v>128</v>
       </c>
       <c r="F14" s="98">
         <f>SUMIF(ConsolidadoRJ[Contrato], D12, ConsolidadoRJ[QDm])</f>
@@ -4276,11 +4273,11 @@
       </c>
       <c r="G14" s="98">
         <f>SUMIF(ConsolidadoRJ[Contrato], D12, ConsolidadoRJ[QNm] )</f>
-        <v>26066</v>
+        <v>34683</v>
       </c>
       <c r="H14" s="99">
         <f>(D14-E14-F14)+G14</f>
-        <v>210989</v>
+        <v>240564</v>
       </c>
       <c r="I14" s="46"/>
       <c r="J14" s="47"/>
@@ -4337,11 +4334,11 @@
       </c>
       <c r="J16" s="40">
         <f>SUMIF(Consolidado!S:S,D15,Consolidado!O:O)</f>
-        <v>992</v>
+        <v>6904</v>
       </c>
       <c r="K16" s="41">
         <f>J16*N5</f>
-        <v>972.16</v>
+        <v>6765.92</v>
       </c>
       <c r="L16" s="42">
         <f>IFERROR(VLOOKUP(ARMCXMID,TabelaIRON[[Linha de Serviço PPU]:[PREÇO UNITÁRIO ]],3,FALSE),"N/A")</f>
@@ -4349,7 +4346,7 @@
       </c>
       <c r="M16" s="43">
         <f>J16*L16</f>
-        <v>3521.6</v>
+        <v>24509.199999999997</v>
       </c>
       <c r="N16" s="151"/>
       <c r="Q16" s="4"/>
@@ -4360,7 +4357,7 @@
       <c r="C17" s="45"/>
       <c r="D17" s="98">
         <f>SUMIF(ConsolidadoRJ[Contrato], D15, ConsolidadoRJ[QUAm-1])</f>
-        <v>110</v>
+        <v>992</v>
       </c>
       <c r="E17" s="98">
         <f>SUMIF(ConsolidadoRJ[Contrato], D15, ConsolidadoRJ[QBm])</f>
@@ -4372,11 +4369,11 @@
       </c>
       <c r="G17" s="98">
         <f>SUMIF(ConsolidadoRJ[Contrato], D15, ConsolidadoRJ[QNm] )</f>
-        <v>882</v>
+        <v>5912</v>
       </c>
       <c r="H17" s="99">
         <f>(D17-E17-F17)+G17</f>
-        <v>992</v>
+        <v>6904</v>
       </c>
       <c r="I17" s="46"/>
       <c r="J17" s="47"/>
@@ -4720,11 +4717,11 @@
       </c>
       <c r="J28" s="40">
         <f>SUMIF(Consolidado!S:S,D27,Consolidado!O:O)</f>
-        <v>5193</v>
+        <v>14650</v>
       </c>
       <c r="K28" s="41">
         <f>J28*N5</f>
-        <v>5089.1400000000003</v>
+        <v>14357</v>
       </c>
       <c r="L28" s="42">
         <f>IFERROR(VLOOKUP(ARMMID,TabelaIRON[[Linha de Serviço PPU]:[PREÇO UNITÁRIO ]],3,FALSE),"N/A")</f>
@@ -4732,7 +4729,7 @@
       </c>
       <c r="M28" s="43">
         <f>J28*L28</f>
-        <v>415.44</v>
+        <v>1172</v>
       </c>
       <c r="N28" s="151"/>
       <c r="Q28" s="4"/>
@@ -4755,11 +4752,11 @@
       </c>
       <c r="G29" s="98">
         <f>SUMIF(ConsolidadoRJ[Contrato], D27, ConsolidadoRJ[QNm] )</f>
-        <v>0</v>
+        <v>9457</v>
       </c>
       <c r="H29" s="100">
         <f>(D29-E29-F29)+G29</f>
-        <v>5193</v>
+        <v>14650</v>
       </c>
       <c r="I29" s="46"/>
       <c r="J29" s="47"/>
@@ -5402,7 +5399,7 @@
       <c r="L48" s="64"/>
       <c r="M48" s="65">
         <f>SUM(M12:M47)</f>
-        <v>189275.65900000001</v>
+        <v>226793.62999999998</v>
       </c>
       <c r="N48" s="56"/>
       <c r="Q48" s="4"/>
@@ -21874,24 +21871,24 @@
         <v>1</v>
       </c>
       <c r="J4" s="131">
-        <v>183910</v>
+        <v>199223</v>
       </c>
       <c r="K4" s="131">
-        <v>1</v>
+        <v>128</v>
       </c>
       <c r="L4" s="131">
         <v>0</v>
       </c>
       <c r="M4" s="131">
-        <v>20282</v>
+        <v>28034</v>
       </c>
       <c r="N4" s="119">
         <f>IF(ConsolidadoRJ[[#This Row],[QUAm-1]]="","",ConsolidadoRJ[[#This Row],[QUAm-1]]+ConsolidadoRJ[[#This Row],[QNm]]-ConsolidadoRJ[[#This Row],[QBm]]-ConsolidadoRJ[[#This Row],[QDm]])</f>
-        <v>204191</v>
+        <v>227129</v>
       </c>
       <c r="O4" s="119">
         <f>IF(ConsolidadoRJ[[#This Row],[FC = V1/V2]]="","",ConsolidadoRJ[[#This Row],[FC = V1/V2]]*ConsolidadoRJ[[#This Row],[QUAm]])</f>
-        <v>204191</v>
+        <v>227129</v>
       </c>
       <c r="P4" s="121">
         <f>IF( ConsolidadoRJ[[#This Row],[Contrato]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[Contrato]],TabelaIRON[[Linha de Serviço PPU]:[PREÇO UNITÁRIO ]],3,0),"Nao Encontrado"))</f>
@@ -21899,7 +21896,7 @@
       </c>
       <c r="Q4" s="121">
         <f>IF(ConsolidadoRJ[[#This Row],[UA]]="","",ConsolidadoRJ[[#This Row],[UA]]*ConsolidadoRJ[[#This Row],[$ Unitário]])</f>
-        <v>122514.59999999999</v>
+        <v>136277.4</v>
       </c>
       <c r="R4" s="122" t="s">
         <v>122</v>
@@ -21944,7 +21941,7 @@
         <v>1</v>
       </c>
       <c r="J5" s="131">
-        <v>110</v>
+        <v>992</v>
       </c>
       <c r="K5" s="131">
         <v>0</v>
@@ -21953,15 +21950,15 @@
         <v>0</v>
       </c>
       <c r="M5" s="131">
-        <v>882</v>
+        <v>5912</v>
       </c>
       <c r="N5" s="119">
         <f>IF(ConsolidadoRJ[[#This Row],[QUAm-1]]="","",ConsolidadoRJ[[#This Row],[QUAm-1]]+ConsolidadoRJ[[#This Row],[QNm]]-ConsolidadoRJ[[#This Row],[QBm]]-ConsolidadoRJ[[#This Row],[QDm]])</f>
-        <v>992</v>
+        <v>6904</v>
       </c>
       <c r="O5" s="119">
         <f>IF(ConsolidadoRJ[[#This Row],[FC = V1/V2]]="","",ConsolidadoRJ[[#This Row],[FC = V1/V2]]*ConsolidadoRJ[[#This Row],[QUAm]])</f>
-        <v>992</v>
+        <v>6904</v>
       </c>
       <c r="P5" s="121">
         <f>IF( ConsolidadoRJ[[#This Row],[Contrato]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[Contrato]],TabelaIRON[[Linha de Serviço PPU]:[PREÇO UNITÁRIO ]],3,0),"Nao Encontrado"))</f>
@@ -21969,7 +21966,7 @@
       </c>
       <c r="Q5" s="121">
         <f>IF(ConsolidadoRJ[[#This Row],[UA]]="","",ConsolidadoRJ[[#This Row],[UA]]*ConsolidadoRJ[[#This Row],[$ Unitário]])</f>
-        <v>3521.6</v>
+        <v>24509.199999999997</v>
       </c>
       <c r="R5" s="122" t="s">
         <v>124</v>
@@ -22084,7 +22081,7 @@
         <v>0.505</v>
       </c>
       <c r="J7" s="131">
-        <v>1014</v>
+        <v>6786</v>
       </c>
       <c r="K7" s="131">
         <v>0</v>
@@ -22093,15 +22090,15 @@
         <v>0</v>
       </c>
       <c r="M7" s="131">
-        <v>5784</v>
+        <v>6649</v>
       </c>
       <c r="N7" s="119">
         <f>IF(ConsolidadoRJ[[#This Row],[QUAm-1]]="","",ConsolidadoRJ[[#This Row],[QUAm-1]]+ConsolidadoRJ[[#This Row],[QNm]]-ConsolidadoRJ[[#This Row],[QBm]]-ConsolidadoRJ[[#This Row],[QDm]])</f>
-        <v>6798</v>
+        <v>13435</v>
       </c>
       <c r="O7" s="119">
         <f>IF(ConsolidadoRJ[[#This Row],[FC = V1/V2]]="","",ConsolidadoRJ[[#This Row],[FC = V1/V2]]*ConsolidadoRJ[[#This Row],[QUAm]])</f>
-        <v>3432.9900000000002</v>
+        <v>6784.6750000000002</v>
       </c>
       <c r="P7" s="121">
         <f>IF( ConsolidadoRJ[[#This Row],[Contrato]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[Contrato]],TabelaIRON[[Linha de Serviço PPU]:[PREÇO UNITÁRIO ]],3,0),"Nao Encontrado"))</f>
@@ -22109,7 +22106,7 @@
       </c>
       <c r="Q7" s="121">
         <f>IF(ConsolidadoRJ[[#This Row],[UA]]="","",ConsolidadoRJ[[#This Row],[UA]]*ConsolidadoRJ[[#This Row],[$ Unitário]])</f>
-        <v>2059.7939999999999</v>
+        <v>4070.8049999999998</v>
       </c>
       <c r="R7" s="122" t="s">
         <v>122</v>
@@ -22303,15 +22300,15 @@
         <v>0</v>
       </c>
       <c r="M10" s="131">
-        <v>0</v>
+        <v>6123</v>
       </c>
       <c r="N10" s="119">
         <f>IF(ConsolidadoRJ[[#This Row],[QUAm-1]]="","",ConsolidadoRJ[[#This Row],[QUAm-1]]+ConsolidadoRJ[[#This Row],[QNm]]-ConsolidadoRJ[[#This Row],[QBm]]-ConsolidadoRJ[[#This Row],[QDm]])</f>
-        <v>0</v>
+        <v>6123</v>
       </c>
       <c r="O10" s="119">
         <f>IF(ConsolidadoRJ[[#This Row],[FC = V1/V2]]="","",ConsolidadoRJ[[#This Row],[FC = V1/V2]]*ConsolidadoRJ[[#This Row],[QUAm]])</f>
-        <v>0</v>
+        <v>6123</v>
       </c>
       <c r="P10" s="121">
         <f>IF( ConsolidadoRJ[[#This Row],[Contrato]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[Contrato]],TabelaIRON[[Linha de Serviço PPU]:[PREÇO UNITÁRIO ]],3,0),"Nao Encontrado"))</f>
@@ -22319,7 +22316,7 @@
       </c>
       <c r="Q10" s="121">
         <f>IF(ConsolidadoRJ[[#This Row],[UA]]="","",ConsolidadoRJ[[#This Row],[UA]]*ConsolidadoRJ[[#This Row],[$ Unitário]])</f>
-        <v>0</v>
+        <v>489.84000000000003</v>
       </c>
       <c r="R10" s="122" t="s">
         <v>134</v>
@@ -22373,15 +22370,15 @@
         <v>0</v>
       </c>
       <c r="M11" s="131">
-        <v>0</v>
+        <v>3334</v>
       </c>
       <c r="N11" s="119">
         <f>IF(ConsolidadoRJ[[#This Row],[QUAm-1]]="","",ConsolidadoRJ[[#This Row],[QUAm-1]]+ConsolidadoRJ[[#This Row],[QNm]]-ConsolidadoRJ[[#This Row],[QBm]]-ConsolidadoRJ[[#This Row],[QDm]])</f>
-        <v>5193</v>
+        <v>8527</v>
       </c>
       <c r="O11" s="119">
         <f>IF(ConsolidadoRJ[[#This Row],[FC = V1/V2]]="","",ConsolidadoRJ[[#This Row],[FC = V1/V2]]*ConsolidadoRJ[[#This Row],[QUAm]])</f>
-        <v>5193</v>
+        <v>8527</v>
       </c>
       <c r="P11" s="121">
         <f>IF( ConsolidadoRJ[[#This Row],[Contrato]] = "", "", IFERROR( VLOOKUP(ConsolidadoRJ[[#This Row],[Contrato]],TabelaIRON[[Linha de Serviço PPU]:[PREÇO UNITÁRIO ]],3,0),"Nao Encontrado"))</f>
@@ -22389,7 +22386,7 @@
       </c>
       <c r="Q11" s="121">
         <f>IF(ConsolidadoRJ[[#This Row],[UA]]="","",ConsolidadoRJ[[#This Row],[UA]]*ConsolidadoRJ[[#This Row],[$ Unitário]])</f>
-        <v>415.44</v>
+        <v>682.16</v>
       </c>
       <c r="R11" s="122" t="s">
         <v>136</v>
